--- a/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
+++ b/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
@@ -1559,19 +1559,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1669,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1743,13 +1743,13 @@
         <v>30.82224430000005</v>
       </c>
       <c r="N4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="O4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="P4" t="n">
-        <v>5.790863699999997</v>
+        <v>5.790863699999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1761,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>26.28542482500007</v>
+        <v>26.28542482500006</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1802,19 +1802,19 @@
         <v>286.6336253666667</v>
       </c>
       <c r="G5" t="n">
-        <v>195.4999999999999</v>
+        <v>195.5</v>
       </c>
       <c r="H5" t="n">
         <v>0.9969865230144929</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0.8663746333332938</v>
       </c>
       <c r="K5" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>30.82224430000005</v>
@@ -1829,7 +1829,7 @@
         <v>304.8397</v>
       </c>
       <c r="P5" t="n">
-        <v>3.658076400000001</v>
+        <v>3.6580764</v>
       </c>
       <c r="Q5" t="n">
         <v>0.012</v>
@@ -1879,22 +1879,22 @@
         <v>241.5</v>
       </c>
       <c r="F6" t="n">
-        <v>368.0000000000001</v>
+        <v>368</v>
       </c>
       <c r="G6" t="n">
-        <v>241.5</v>
+        <v>241.4999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L6" t="n">
         <v>45.37024253333334</v>
@@ -1903,13 +1903,13 @@
         <v>55.29486493333332</v>
       </c>
       <c r="N6" t="n">
-        <v>412.5148000000001</v>
+        <v>412.5148</v>
       </c>
       <c r="O6" t="n">
-        <v>382.5148000000001</v>
+        <v>382.5148</v>
       </c>
       <c r="P6" t="n">
-        <v>4.590177600000001</v>
+        <v>4.5901776</v>
       </c>
       <c r="Q6" t="n">
         <v>0.012</v>
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1965,13 +1965,13 @@
         <v>287.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J50" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K50" t="n">
         <v>0.3825148</v>
@@ -5653,7 +5653,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J51" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K51" t="n">
         <v>0.3825148</v>
@@ -5724,7 +5724,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J52" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K52" t="n">
         <v>0.3825148</v>
@@ -5795,7 +5795,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J53" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K53" t="n">
         <v>0.3825148</v>
@@ -5866,7 +5866,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J54" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K54" t="n">
         <v>0.3825148</v>
@@ -5937,7 +5937,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J55" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K55" t="n">
         <v>0.3825148</v>
@@ -6008,7 +6008,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J56" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K56" t="n">
         <v>0.3825148</v>
@@ -6079,7 +6079,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J57" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K57" t="n">
         <v>0.3825148</v>
@@ -6150,7 +6150,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J58" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K58" t="n">
         <v>0.3825148</v>
@@ -6221,7 +6221,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J59" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K59" t="n">
         <v>0.3825148</v>
@@ -6292,7 +6292,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J60" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K60" t="n">
         <v>0.3825148</v>
@@ -6363,7 +6363,7 @@
         <v>34.37623333333333</v>
       </c>
       <c r="J61" t="n">
-        <v>31.87623333333334</v>
+        <v>31.87623333333333</v>
       </c>
       <c r="K61" t="n">
         <v>0.3825148</v>
@@ -8620,10 +8620,10 @@
         <v>161.7714</v>
       </c>
       <c r="M18" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="N18" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -10369,7 +10369,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0.99</v>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0.99</v>
@@ -10504,7 +10504,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -10729,7 +10729,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>0.97</v>
@@ -23589,7 +23589,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.866374633333308</v>
+        <v>0.8663746333333506</v>
       </c>
     </row>
     <row r="9">
@@ -23609,7 +23609,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="10">
@@ -23629,7 +23629,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.127311245430624</v>
+        <v>9.127311245430626</v>
       </c>
     </row>
     <row r="11">
@@ -23649,7 +23649,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.263007537570009</v>
+        <v>7.26300753757001</v>
       </c>
     </row>
     <row r="12">
@@ -23689,7 +23689,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9999999999999997</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="14">

--- a/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
+++ b/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>1 / 0 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -774,7 +918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,7 +933,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -807,7 +951,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -822,7 +966,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -839,7 +983,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -854,7 +998,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -871,7 +1015,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -886,7 +1030,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -903,7 +1047,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -918,7 +1062,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -935,7 +1079,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -950,7 +1094,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -967,7 +1111,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -982,7 +1126,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -999,7 +1143,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1014,7 +1158,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1175,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1046,7 +1190,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1207,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1078,7 +1222,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1239,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1110,7 +1254,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1271,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1142,7 +1286,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1303,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1174,7 +1318,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1335,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1206,7 +1350,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1367,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1238,7 +1382,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1399,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,7 +1414,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1302,7 +1446,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1463,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1334,7 +1478,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1495,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1366,7 +1510,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1527,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1398,7 +1542,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -1820,16 +1964,16 @@
         <v>30.82224430000005</v>
       </c>
       <c r="M5" t="n">
-        <v>45.37024253333334</v>
+        <v>45.37903573333334</v>
       </c>
       <c r="N5" t="n">
-        <v>349.8397</v>
+        <v>349.8486</v>
       </c>
       <c r="O5" t="n">
-        <v>304.8397</v>
+        <v>304.8486</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6580764</v>
+        <v>3.6581832</v>
       </c>
       <c r="Q5" t="n">
         <v>0.012</v>
@@ -1841,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>19.62372214861113</v>
+        <v>19.62540586527779</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1852,10 +1996,10 @@
         <v>120</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1363140869565218</v>
+        <v>0.1363478260869565</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-4.263256414560601e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1897,10 +2041,10 @@
         <v>2.842170943040401e-14</v>
       </c>
       <c r="L6" t="n">
-        <v>45.37024253333334</v>
+        <v>45.37903573333334</v>
       </c>
       <c r="M6" t="n">
-        <v>55.29486493333332</v>
+        <v>55.30365813333331</v>
       </c>
       <c r="N6" t="n">
         <v>412.5148</v>
@@ -1921,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>50.33255373333333</v>
+        <v>50.34134693333332</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1935,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.4210854715202e-14</v>
       </c>
     </row>
     <row r="7">
@@ -1977,19 +2121,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>55.29486493333332</v>
+        <v>55.30365813333331</v>
       </c>
       <c r="M7" t="n">
-        <v>55.29469853333337</v>
+        <v>55.30230613333334</v>
       </c>
       <c r="N7" t="n">
-        <v>453.9472</v>
+        <v>453.946</v>
       </c>
       <c r="O7" t="n">
-        <v>453.9472</v>
+        <v>453.946</v>
       </c>
       <c r="P7" t="n">
-        <v>5.4473664</v>
+        <v>5.447352</v>
       </c>
       <c r="Q7" t="n">
         <v>0.012</v>
@@ -2001,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>55.29478173333334</v>
+        <v>55.30298213333333</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2012,10 +2156,10 @@
         <v>120</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07569096989966556</v>
+        <v>0.07568963210702342</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>1.06581410364015e-13</v>
       </c>
     </row>
   </sheetData>
@@ -5011,16 +5155,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>30.14765</v>
+        <v>30.14755</v>
       </c>
       <c r="J42" t="n">
-        <v>25.64765</v>
+        <v>25.64755</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3077718</v>
+        <v>0.3077706</v>
       </c>
       <c r="L42" t="n">
-        <v>25.3398782</v>
+        <v>25.3397794</v>
       </c>
       <c r="M42" t="n">
         <v>23.95833333333333</v>
@@ -5041,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.381544866666665</v>
+        <v>1.381446066666665</v>
       </c>
       <c r="T42" t="n">
-        <v>0.04144634599999996</v>
+        <v>0.04144338199999997</v>
       </c>
       <c r="U42" t="n">
         <v>13.48095</v>
@@ -5079,19 +5223,19 @@
         <v>0.012</v>
       </c>
       <c r="H43" t="n">
-        <v>1.381544866666665</v>
+        <v>1.381446066666665</v>
       </c>
       <c r="I43" t="n">
-        <v>30.14765</v>
+        <v>30.14755</v>
       </c>
       <c r="J43" t="n">
-        <v>25.64765</v>
+        <v>25.64755</v>
       </c>
       <c r="K43" t="n">
-        <v>0.3077718</v>
+        <v>0.3077706</v>
       </c>
       <c r="L43" t="n">
-        <v>26.72142306666666</v>
+        <v>26.72122546666666</v>
       </c>
       <c r="M43" t="n">
         <v>23.95833333333333</v>
@@ -5112,10 +5256,10 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.763089733333331</v>
+        <v>2.762892133333331</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1243390379999999</v>
+        <v>0.1243301459999999</v>
       </c>
       <c r="U43" t="n">
         <v>13.48095</v>
@@ -5150,19 +5294,19 @@
         <v>0.012</v>
       </c>
       <c r="H44" t="n">
-        <v>2.763089733333331</v>
+        <v>2.762892133333331</v>
       </c>
       <c r="I44" t="n">
-        <v>39.31435</v>
+        <v>39.31415</v>
       </c>
       <c r="J44" t="n">
-        <v>34.81435</v>
+        <v>34.81415</v>
       </c>
       <c r="K44" t="n">
-        <v>0.4177722</v>
+        <v>0.4177698</v>
       </c>
       <c r="L44" t="n">
-        <v>37.15966753333333</v>
+        <v>37.15927233333333</v>
       </c>
       <c r="M44" t="n">
         <v>23.95833333333333</v>
@@ -5183,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>13.20133419999999</v>
+        <v>13.20093899999999</v>
       </c>
       <c r="T44" t="n">
-        <v>0.4789327179999998</v>
+        <v>0.4789149339999998</v>
       </c>
       <c r="U44" t="n">
         <v>13.48095</v>
@@ -5221,19 +5365,19 @@
         <v>0.012</v>
       </c>
       <c r="H45" t="n">
-        <v>13.20133419999999</v>
+        <v>13.20093899999999</v>
       </c>
       <c r="I45" t="n">
-        <v>39.31435</v>
+        <v>39.31415</v>
       </c>
       <c r="J45" t="n">
-        <v>34.81435</v>
+        <v>34.81415</v>
       </c>
       <c r="K45" t="n">
-        <v>0.4177722</v>
+        <v>0.4177698</v>
       </c>
       <c r="L45" t="n">
-        <v>47.59791199999999</v>
+        <v>47.59731919999999</v>
       </c>
       <c r="M45" t="n">
         <v>23.95833333333333</v>
@@ -5254,10 +5398,10 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>23.63957866666666</v>
+        <v>23.63898586666665</v>
       </c>
       <c r="T45" t="n">
-        <v>1.105227386</v>
+        <v>1.105197745999999</v>
       </c>
       <c r="U45" t="n">
         <v>13.48095</v>
@@ -5292,19 +5436,19 @@
         <v>0.012</v>
       </c>
       <c r="H46" t="n">
-        <v>23.63957866666666</v>
+        <v>23.63898586666665</v>
       </c>
       <c r="I46" t="n">
-        <v>39.31435</v>
+        <v>39.31415</v>
       </c>
       <c r="J46" t="n">
-        <v>34.81435</v>
+        <v>34.81415</v>
       </c>
       <c r="K46" t="n">
-        <v>0.4177722</v>
+        <v>0.4177698</v>
       </c>
       <c r="L46" t="n">
-        <v>58.03615646666665</v>
+        <v>58.03536606666665</v>
       </c>
       <c r="M46" t="n">
         <v>23.95833333333333</v>
@@ -5325,10 +5469,10 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>34.07782313333333</v>
+        <v>34.07703273333333</v>
       </c>
       <c r="T46" t="n">
-        <v>1.731522054</v>
+        <v>1.731480557999999</v>
       </c>
       <c r="U46" t="n">
         <v>13.48095</v>
@@ -5363,19 +5507,19 @@
         <v>0.012</v>
       </c>
       <c r="H47" t="n">
-        <v>34.07782313333333</v>
+        <v>34.07703273333333</v>
       </c>
       <c r="I47" t="n">
-        <v>38.50465</v>
+        <v>38.51455</v>
       </c>
       <c r="J47" t="n">
-        <v>34.00465</v>
+        <v>34.01455</v>
       </c>
       <c r="K47" t="n">
-        <v>0.4080558</v>
+        <v>0.4081746</v>
       </c>
       <c r="L47" t="n">
-        <v>67.67441733333332</v>
+        <v>67.68340813333333</v>
       </c>
       <c r="M47" t="n">
         <v>23.95833333333333</v>
@@ -5396,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>43.716084</v>
+        <v>43.7250748</v>
       </c>
       <c r="T47" t="n">
-        <v>2.333817213999999</v>
+        <v>2.334063226</v>
       </c>
       <c r="U47" t="n">
         <v>13.48095</v>
@@ -5434,19 +5578,19 @@
         <v>0.012</v>
       </c>
       <c r="H48" t="n">
-        <v>43.716084</v>
+        <v>43.7250748</v>
       </c>
       <c r="I48" t="n">
-        <v>29.58645</v>
+        <v>29.58635</v>
       </c>
       <c r="J48" t="n">
-        <v>25.08645</v>
+        <v>25.08635</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3010374</v>
+        <v>0.3010362</v>
       </c>
       <c r="L48" t="n">
-        <v>68.5014966</v>
+        <v>68.5103886</v>
       </c>
       <c r="M48" t="n">
         <v>23.95833333333333</v>
@@ -5467,10 +5611,10 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>44.54316326666667</v>
+        <v>44.55205526666667</v>
       </c>
       <c r="T48" t="n">
-        <v>2.647777418</v>
+        <v>2.648313902</v>
       </c>
       <c r="U48" t="n">
         <v>13.48095</v>
@@ -5505,19 +5649,19 @@
         <v>0.012</v>
       </c>
       <c r="H49" t="n">
-        <v>44.54316326666667</v>
+        <v>44.55205526666667</v>
       </c>
       <c r="I49" t="n">
-        <v>29.58645</v>
+        <v>29.58635</v>
       </c>
       <c r="J49" t="n">
-        <v>25.08645</v>
+        <v>25.08635</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3010374</v>
+        <v>0.3010362</v>
       </c>
       <c r="L49" t="n">
-        <v>69.32857586666667</v>
+        <v>69.33736906666667</v>
       </c>
       <c r="M49" t="n">
         <v>23.95833333333333</v>
@@ -5538,10 +5682,10 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>45.37024253333334</v>
+        <v>45.37903573333334</v>
       </c>
       <c r="T49" t="n">
-        <v>2.697402174</v>
+        <v>2.69793273</v>
       </c>
       <c r="U49" t="n">
         <v>13.48095</v>
@@ -5576,7 +5720,7 @@
         <v>0.012</v>
       </c>
       <c r="H50" t="n">
-        <v>45.37024253333334</v>
+        <v>45.37903573333334</v>
       </c>
       <c r="I50" t="n">
         <v>34.37623333333333</v>
@@ -5588,7 +5732,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L50" t="n">
-        <v>76.86396106666668</v>
+        <v>76.87275426666667</v>
       </c>
       <c r="M50" t="n">
         <v>30.66666666666667</v>
@@ -5609,10 +5753,10 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>46.1972944</v>
+        <v>46.2060876</v>
       </c>
       <c r="T50" t="n">
-        <v>2.747026108</v>
+        <v>2.747553700000001</v>
       </c>
       <c r="U50" t="n">
         <v>15.83333333333333</v>
@@ -5647,7 +5791,7 @@
         <v>0.012</v>
       </c>
       <c r="H51" t="n">
-        <v>46.1972944</v>
+        <v>46.2060876</v>
       </c>
       <c r="I51" t="n">
         <v>34.37623333333333</v>
@@ -5659,7 +5803,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L51" t="n">
-        <v>77.69101293333334</v>
+        <v>77.69980613333334</v>
       </c>
       <c r="M51" t="n">
         <v>30.66666666666667</v>
@@ -5680,10 +5824,10 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>47.02434626666667</v>
+        <v>47.03313946666667</v>
       </c>
       <c r="T51" t="n">
-        <v>2.79664922</v>
+        <v>2.797176812</v>
       </c>
       <c r="U51" t="n">
         <v>15.83333333333333</v>
@@ -5718,7 +5862,7 @@
         <v>0.012</v>
       </c>
       <c r="H52" t="n">
-        <v>47.02434626666667</v>
+        <v>47.03313946666667</v>
       </c>
       <c r="I52" t="n">
         <v>34.37623333333333</v>
@@ -5730,7 +5874,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L52" t="n">
-        <v>78.5180648</v>
+        <v>78.526858</v>
       </c>
       <c r="M52" t="n">
         <v>30.66666666666667</v>
@@ -5751,10 +5895,10 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>47.85139813333333</v>
+        <v>47.86019133333333</v>
       </c>
       <c r="T52" t="n">
-        <v>2.846272332</v>
+        <v>2.846799924</v>
       </c>
       <c r="U52" t="n">
         <v>15.83333333333333</v>
@@ -5789,7 +5933,7 @@
         <v>0.012</v>
       </c>
       <c r="H53" t="n">
-        <v>47.85139813333333</v>
+        <v>47.86019133333333</v>
       </c>
       <c r="I53" t="n">
         <v>34.37623333333333</v>
@@ -5801,7 +5945,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L53" t="n">
-        <v>79.34511666666667</v>
+        <v>79.35390986666667</v>
       </c>
       <c r="M53" t="n">
         <v>30.66666666666667</v>
@@ -5822,10 +5966,10 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>48.67845</v>
+        <v>48.6872432</v>
       </c>
       <c r="T53" t="n">
-        <v>2.895895444</v>
+        <v>2.896423036</v>
       </c>
       <c r="U53" t="n">
         <v>15.83333333333333</v>
@@ -5860,7 +6004,7 @@
         <v>0.012</v>
       </c>
       <c r="H54" t="n">
-        <v>48.67845</v>
+        <v>48.6872432</v>
       </c>
       <c r="I54" t="n">
         <v>34.37623333333333</v>
@@ -5872,7 +6016,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L54" t="n">
-        <v>80.17216853333333</v>
+        <v>80.18096173333333</v>
       </c>
       <c r="M54" t="n">
         <v>30.66666666666667</v>
@@ -5893,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>49.50550186666666</v>
+        <v>49.51429506666666</v>
       </c>
       <c r="T54" t="n">
-        <v>2.945518556</v>
+        <v>2.946046147999999</v>
       </c>
       <c r="U54" t="n">
         <v>15.83333333333333</v>
@@ -5931,7 +6075,7 @@
         <v>0.012</v>
       </c>
       <c r="H55" t="n">
-        <v>49.50550186666666</v>
+        <v>49.51429506666666</v>
       </c>
       <c r="I55" t="n">
         <v>34.37623333333333</v>
@@ -5943,7 +6087,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L55" t="n">
-        <v>80.9992204</v>
+        <v>81.0080136</v>
       </c>
       <c r="M55" t="n">
         <v>30.66666666666667</v>
@@ -5964,10 +6108,10 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>50.33255373333333</v>
+        <v>50.34134693333333</v>
       </c>
       <c r="T55" t="n">
-        <v>2.995141667999999</v>
+        <v>2.99566926</v>
       </c>
       <c r="U55" t="n">
         <v>15.83333333333333</v>
@@ -6002,7 +6146,7 @@
         <v>0.012</v>
       </c>
       <c r="H56" t="n">
-        <v>50.33255373333333</v>
+        <v>50.34134693333333</v>
       </c>
       <c r="I56" t="n">
         <v>34.37623333333333</v>
@@ -6014,7 +6158,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L56" t="n">
-        <v>81.82627226666666</v>
+        <v>81.83506546666666</v>
       </c>
       <c r="M56" t="n">
         <v>30.66666666666667</v>
@@ -6035,10 +6179,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>51.15960559999999</v>
+        <v>51.16839879999999</v>
       </c>
       <c r="T56" t="n">
-        <v>3.04476478</v>
+        <v>3.045292371999999</v>
       </c>
       <c r="U56" t="n">
         <v>15.83333333333333</v>
@@ -6073,7 +6217,7 @@
         <v>0.012</v>
       </c>
       <c r="H57" t="n">
-        <v>51.15960559999999</v>
+        <v>51.16839879999999</v>
       </c>
       <c r="I57" t="n">
         <v>34.37623333333333</v>
@@ -6085,7 +6229,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L57" t="n">
-        <v>82.65332413333333</v>
+        <v>82.66211733333333</v>
       </c>
       <c r="M57" t="n">
         <v>30.66666666666667</v>
@@ -6106,10 +6250,10 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>51.98665746666666</v>
+        <v>51.99545066666666</v>
       </c>
       <c r="T57" t="n">
-        <v>3.094387891999999</v>
+        <v>3.094915483999999</v>
       </c>
       <c r="U57" t="n">
         <v>15.83333333333333</v>
@@ -6144,7 +6288,7 @@
         <v>0.012</v>
       </c>
       <c r="H58" t="n">
-        <v>51.98665746666666</v>
+        <v>51.99545066666666</v>
       </c>
       <c r="I58" t="n">
         <v>34.37623333333333</v>
@@ -6156,7 +6300,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L58" t="n">
-        <v>83.48037599999999</v>
+        <v>83.48916919999999</v>
       </c>
       <c r="M58" t="n">
         <v>30.66666666666667</v>
@@ -6177,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>52.81370933333332</v>
+        <v>52.82250253333332</v>
       </c>
       <c r="T58" t="n">
-        <v>3.144011003999999</v>
+        <v>3.144538595999999</v>
       </c>
       <c r="U58" t="n">
         <v>15.83333333333333</v>
@@ -6215,7 +6359,7 @@
         <v>0.012</v>
       </c>
       <c r="H59" t="n">
-        <v>52.81370933333332</v>
+        <v>52.82250253333332</v>
       </c>
       <c r="I59" t="n">
         <v>34.37623333333333</v>
@@ -6227,7 +6371,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L59" t="n">
-        <v>84.30742786666666</v>
+        <v>84.31622106666666</v>
       </c>
       <c r="M59" t="n">
         <v>30.66666666666667</v>
@@ -6248,10 +6392,10 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>53.64076119999999</v>
+        <v>53.64955439999999</v>
       </c>
       <c r="T59" t="n">
-        <v>3.193634115999999</v>
+        <v>3.194161707999999</v>
       </c>
       <c r="U59" t="n">
         <v>15.83333333333333</v>
@@ -6286,7 +6430,7 @@
         <v>0.012</v>
       </c>
       <c r="H60" t="n">
-        <v>53.64076119999999</v>
+        <v>53.64955439999999</v>
       </c>
       <c r="I60" t="n">
         <v>34.37623333333333</v>
@@ -6298,7 +6442,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L60" t="n">
-        <v>85.13447973333332</v>
+        <v>85.14327293333332</v>
       </c>
       <c r="M60" t="n">
         <v>30.66666666666667</v>
@@ -6319,10 +6463,10 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>54.46781306666665</v>
+        <v>54.47660626666665</v>
       </c>
       <c r="T60" t="n">
-        <v>3.243257227999999</v>
+        <v>3.243784819999999</v>
       </c>
       <c r="U60" t="n">
         <v>15.83333333333333</v>
@@ -6357,7 +6501,7 @@
         <v>0.012</v>
       </c>
       <c r="H61" t="n">
-        <v>54.46781306666665</v>
+        <v>54.47660626666665</v>
       </c>
       <c r="I61" t="n">
         <v>34.37623333333333</v>
@@ -6369,7 +6513,7 @@
         <v>0.3825148</v>
       </c>
       <c r="L61" t="n">
-        <v>85.96153159999999</v>
+        <v>85.97032479999999</v>
       </c>
       <c r="M61" t="n">
         <v>30.66666666666667</v>
@@ -6390,10 +6534,10 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>55.29486493333332</v>
+        <v>55.30365813333331</v>
       </c>
       <c r="T61" t="n">
-        <v>3.292880339999999</v>
+        <v>3.293407931999999</v>
       </c>
       <c r="U61" t="n">
         <v>15.83333333333333</v>
@@ -6428,19 +6572,19 @@
         <v>0.012</v>
       </c>
       <c r="H62" t="n">
-        <v>55.29486493333332</v>
+        <v>55.30365813333331</v>
       </c>
       <c r="I62" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J62" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L62" t="n">
-        <v>92.66985106666665</v>
+        <v>92.67854546666665</v>
       </c>
       <c r="M62" t="n">
         <v>37.37499999999999</v>
@@ -6461,10 +6605,10 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>55.29485106666666</v>
+        <v>55.30354546666666</v>
       </c>
       <c r="T62" t="n">
-        <v>3.317691479999999</v>
+        <v>3.318216107999998</v>
       </c>
       <c r="U62" t="n">
         <v>15.83333333333333</v>
@@ -6499,19 +6643,19 @@
         <v>0.012</v>
       </c>
       <c r="H63" t="n">
-        <v>55.29485106666666</v>
+        <v>55.30354546666666</v>
       </c>
       <c r="I63" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J63" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L63" t="n">
-        <v>92.66983719999999</v>
+        <v>92.6784328</v>
       </c>
       <c r="M63" t="n">
         <v>37.37499999999999</v>
@@ -6532,10 +6676,10 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>55.2948372</v>
+        <v>55.3034328</v>
       </c>
       <c r="T63" t="n">
-        <v>3.317690648</v>
+        <v>3.318209348</v>
       </c>
       <c r="U63" t="n">
         <v>15.83333333333333</v>
@@ -6570,19 +6714,19 @@
         <v>0.012</v>
       </c>
       <c r="H64" t="n">
-        <v>55.2948372</v>
+        <v>55.3034328</v>
       </c>
       <c r="I64" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J64" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L64" t="n">
-        <v>92.66982333333333</v>
+        <v>92.67832013333333</v>
       </c>
       <c r="M64" t="n">
         <v>37.37499999999999</v>
@@ -6603,10 +6747,10 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>55.29482333333333</v>
+        <v>55.30332013333334</v>
       </c>
       <c r="T64" t="n">
-        <v>3.317689816</v>
+        <v>3.318202588</v>
       </c>
       <c r="U64" t="n">
         <v>15.83333333333333</v>
@@ -6641,19 +6785,19 @@
         <v>0.012</v>
       </c>
       <c r="H65" t="n">
-        <v>55.29482333333333</v>
+        <v>55.30332013333334</v>
       </c>
       <c r="I65" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J65" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L65" t="n">
-        <v>92.66980946666666</v>
+        <v>92.67820746666666</v>
       </c>
       <c r="M65" t="n">
         <v>37.37499999999999</v>
@@ -6674,10 +6818,10 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>55.29480946666667</v>
+        <v>55.30320746666667</v>
       </c>
       <c r="T65" t="n">
-        <v>3.317688984</v>
+        <v>3.318195828</v>
       </c>
       <c r="U65" t="n">
         <v>15.83333333333333</v>
@@ -6712,19 +6856,19 @@
         <v>0.012</v>
       </c>
       <c r="H66" t="n">
-        <v>55.29480946666667</v>
+        <v>55.30320746666667</v>
       </c>
       <c r="I66" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J66" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L66" t="n">
-        <v>92.6697956</v>
+        <v>92.6780948</v>
       </c>
       <c r="M66" t="n">
         <v>37.37499999999999</v>
@@ -6745,10 +6889,10 @@
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>55.29479560000001</v>
+        <v>55.3030948</v>
       </c>
       <c r="T66" t="n">
-        <v>3.317688152</v>
+        <v>3.318189068</v>
       </c>
       <c r="U66" t="n">
         <v>15.83333333333333</v>
@@ -6783,19 +6927,19 @@
         <v>0.012</v>
       </c>
       <c r="H67" t="n">
-        <v>55.29479560000001</v>
+        <v>55.3030948</v>
       </c>
       <c r="I67" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J67" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L67" t="n">
-        <v>92.66978173333334</v>
+        <v>92.67798213333333</v>
       </c>
       <c r="M67" t="n">
         <v>37.37499999999999</v>
@@ -6816,10 +6960,10 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>55.29478173333334</v>
+        <v>55.30298213333334</v>
       </c>
       <c r="T67" t="n">
-        <v>3.317687320000001</v>
+        <v>3.318182308</v>
       </c>
       <c r="U67" t="n">
         <v>15.83333333333333</v>
@@ -6854,19 +6998,19 @@
         <v>0.012</v>
       </c>
       <c r="H68" t="n">
-        <v>55.29478173333334</v>
+        <v>55.30298213333334</v>
       </c>
       <c r="I68" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J68" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L68" t="n">
-        <v>92.66976786666667</v>
+        <v>92.67786946666666</v>
       </c>
       <c r="M68" t="n">
         <v>37.37499999999999</v>
@@ -6887,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>55.29476786666668</v>
+        <v>55.30286946666667</v>
       </c>
       <c r="T68" t="n">
-        <v>3.317686488000001</v>
+        <v>3.318175548</v>
       </c>
       <c r="U68" t="n">
         <v>15.83333333333333</v>
@@ -6925,19 +7069,19 @@
         <v>0.012</v>
       </c>
       <c r="H69" t="n">
-        <v>55.29476786666668</v>
+        <v>55.30286946666667</v>
       </c>
       <c r="I69" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J69" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L69" t="n">
-        <v>92.66975400000001</v>
+        <v>92.6777568</v>
       </c>
       <c r="M69" t="n">
         <v>37.37499999999999</v>
@@ -6958,10 +7102,10 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>55.29475400000002</v>
+        <v>55.3027568</v>
       </c>
       <c r="T69" t="n">
-        <v>3.317685656000001</v>
+        <v>3.318168788</v>
       </c>
       <c r="U69" t="n">
         <v>15.83333333333333</v>
@@ -6996,19 +7140,19 @@
         <v>0.012</v>
       </c>
       <c r="H70" t="n">
-        <v>55.29475400000002</v>
+        <v>55.3027568</v>
       </c>
       <c r="I70" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J70" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K70" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L70" t="n">
-        <v>92.66974013333335</v>
+        <v>92.67764413333333</v>
       </c>
       <c r="M70" t="n">
         <v>37.37499999999999</v>
@@ -7029,10 +7173,10 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>55.29474013333336</v>
+        <v>55.30264413333334</v>
       </c>
       <c r="T70" t="n">
-        <v>3.317684824000001</v>
+        <v>3.318162028</v>
       </c>
       <c r="U70" t="n">
         <v>15.83333333333333</v>
@@ -7067,19 +7211,19 @@
         <v>0.012</v>
       </c>
       <c r="H71" t="n">
-        <v>55.29474013333336</v>
+        <v>55.30264413333334</v>
       </c>
       <c r="I71" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J71" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K71" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L71" t="n">
-        <v>92.66972626666669</v>
+        <v>92.67753146666666</v>
       </c>
       <c r="M71" t="n">
         <v>37.37499999999999</v>
@@ -7100,10 +7244,10 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>55.29472626666669</v>
+        <v>55.30253146666667</v>
       </c>
       <c r="T71" t="n">
-        <v>3.317683992000001</v>
+        <v>3.318155268</v>
       </c>
       <c r="U71" t="n">
         <v>15.83333333333333</v>
@@ -7138,19 +7282,19 @@
         <v>0.012</v>
       </c>
       <c r="H72" t="n">
-        <v>55.29472626666669</v>
+        <v>55.30253146666667</v>
       </c>
       <c r="I72" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J72" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L72" t="n">
-        <v>92.66971240000002</v>
+        <v>92.6774188</v>
       </c>
       <c r="M72" t="n">
         <v>37.37499999999999</v>
@@ -7171,10 +7315,10 @@
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>55.29471240000003</v>
+        <v>55.30241880000001</v>
       </c>
       <c r="T72" t="n">
-        <v>3.317683160000001</v>
+        <v>3.318148508</v>
       </c>
       <c r="U72" t="n">
         <v>15.83333333333333</v>
@@ -7209,19 +7353,19 @@
         <v>0.012</v>
       </c>
       <c r="H73" t="n">
-        <v>55.29471240000003</v>
+        <v>55.30241880000001</v>
       </c>
       <c r="I73" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="J73" t="n">
-        <v>37.82893333333333</v>
+        <v>37.82883333333334</v>
       </c>
       <c r="K73" t="n">
-        <v>0.4539472</v>
+        <v>0.453946</v>
       </c>
       <c r="L73" t="n">
-        <v>92.66969853333336</v>
+        <v>92.67730613333333</v>
       </c>
       <c r="M73" t="n">
         <v>37.37499999999999</v>
@@ -7242,10 +7386,10 @@
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>55.29469853333337</v>
+        <v>55.30230613333334</v>
       </c>
       <c r="T73" t="n">
-        <v>3.317682328000002</v>
+        <v>3.318141748</v>
       </c>
       <c r="U73" t="n">
         <v>15.83333333333333</v>
@@ -8692,13 +8836,13 @@
         <v>110</v>
       </c>
       <c r="L19" t="n">
-        <v>48.8776</v>
+        <v>48.87720000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>48.8778</v>
+        <v>48.8772</v>
       </c>
       <c r="N19" t="n">
-        <v>48.8778</v>
+        <v>48.8772</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -8710,13 +8854,13 @@
         <v>1.25</v>
       </c>
       <c r="R19" t="n">
-        <v>48.8776</v>
+        <v>48.87720000000001</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>543.7633</v>
+        <v>543.7588500000001</v>
       </c>
       <c r="U19" t="n">
         <v>16.5</v>
@@ -8917,13 +9061,13 @@
         <v>80</v>
       </c>
       <c r="L22" t="n">
-        <v>39.1903</v>
+        <v>39.2</v>
       </c>
       <c r="M22" t="n">
-        <v>39.1905</v>
+        <v>39.2</v>
       </c>
       <c r="N22" t="n">
-        <v>39.1905</v>
+        <v>39.2</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -8935,13 +9079,13 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>39.1903</v>
+        <v>39.2</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>540.82614</v>
+        <v>540.9599999999999</v>
       </c>
       <c r="U22" t="n">
         <v>28</v>
@@ -9442,13 +9586,13 @@
         <v>110</v>
       </c>
       <c r="L29" t="n">
-        <v>110</v>
+        <v>109.9992</v>
       </c>
       <c r="M29" t="n">
-        <v>110.0004</v>
+        <v>109.9992</v>
       </c>
       <c r="N29" t="n">
-        <v>110.0004</v>
+        <v>109.9992</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -9460,13 +9604,13 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>110</v>
+        <v>109.9992</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>979</v>
+        <v>978.9928800000001</v>
       </c>
       <c r="U29" t="n">
         <v>16.5</v>
@@ -9667,7 +9811,7 @@
         <v>33.948</v>
       </c>
       <c r="L32" t="n">
-        <v>33.9474</v>
+        <v>33.9468</v>
       </c>
       <c r="M32" t="n">
         <v>33.9468</v>
@@ -9685,13 +9829,13 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>33.9474</v>
+        <v>33.9468</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>468.47412</v>
+        <v>468.4658400000001</v>
       </c>
       <c r="U32" t="n">
         <v>11.8818</v>
@@ -9914,13 +10058,13 @@
         <v>2038</v>
       </c>
       <c r="D5" t="n">
-        <v>2638.31779</v>
+        <v>2638.4472</v>
       </c>
       <c r="E5" t="n">
         <v>117.2974</v>
       </c>
       <c r="F5" t="n">
-        <v>14.12907994700001</v>
+        <v>14.13029222300001</v>
       </c>
       <c r="G5" t="n">
         <v>82</v>
@@ -9929,13 +10073,13 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2851.744269947</v>
+        <v>2851.874892223</v>
       </c>
       <c r="J5" t="n">
         <v>0.7938322410201696</v>
       </c>
       <c r="K5" t="n">
-        <v>2263.806544628455</v>
+        <v>2263.910236802539</v>
       </c>
       <c r="L5" t="n">
         <v>1430</v>
@@ -9962,7 +10106,7 @@
         <v>100.8774</v>
       </c>
       <c r="F6" t="n">
-        <v>36.23943868799999</v>
+        <v>36.245769792</v>
       </c>
       <c r="G6" t="n">
         <v>82</v>
@@ -9971,13 +10115,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3192.093988688</v>
+        <v>3192.100319792</v>
       </c>
       <c r="J6" t="n">
         <v>0.7350298527964533</v>
       </c>
       <c r="K6" t="n">
-        <v>2346.284374617784</v>
+        <v>2346.289028168225</v>
       </c>
       <c r="L6" t="n">
         <v>1430</v>
@@ -9998,13 +10142,13 @@
         <v>2040</v>
       </c>
       <c r="D7" t="n">
-        <v>2985.47412</v>
+        <v>2985.45872</v>
       </c>
       <c r="E7" t="n">
         <v>113.8818</v>
       </c>
       <c r="F7" t="n">
-        <v>39.812242848</v>
+        <v>39.818147136</v>
       </c>
       <c r="G7" t="n">
         <v>82</v>
@@ -10013,13 +10157,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3221.168162848</v>
+        <v>3221.158667136</v>
       </c>
       <c r="J7" t="n">
         <v>0.6805831970337529</v>
       </c>
       <c r="K7" t="n">
-        <v>2192.272926454432</v>
+        <v>2192.266463832401</v>
       </c>
       <c r="L7" t="n">
         <v>1430</v>
@@ -10119,7 +10263,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2038-01: physical stock 30.822 t &lt; 45-day reserve 35.445 t</t>
+          <t>2038-01: физический запас 30.822 т &lt; 45-дневного резерва 35.445 т</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -11411,7 +11555,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>45.37024253333334</v>
+        <v>45.37903573333334</v>
       </c>
       <c r="G27" t="n">
         <v>45.36986301369863</v>
@@ -11460,7 +11604,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>55.29486493333332</v>
+        <v>55.30365813333331</v>
       </c>
       <c r="G28" t="n">
         <v>55.2945205479452</v>
@@ -11516,7 +11660,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11529,7 +11673,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11709,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11578,7 +11722,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11614,7 +11758,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11627,7 +11771,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11656,14 +11800,14 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.1363140869565218</v>
+        <v>0.1363478260869565</v>
       </c>
       <c r="G32" t="n">
         <v>0.2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11676,7 +11820,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11856,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11725,7 +11869,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11754,14 +11898,14 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.07569096989966556</v>
+        <v>0.07568963210702342</v>
       </c>
       <c r="G34" t="n">
         <v>0.2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11774,7 +11918,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12741,7 +12885,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>45.37024253333334</v>
+        <v>45.37903573333334</v>
       </c>
       <c r="G55" t="n">
         <v>120</v>
@@ -12937,7 +13081,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>48.8776</v>
+        <v>48.87720000000001</v>
       </c>
       <c r="G59" t="n">
         <v>110</v>
@@ -13133,7 +13277,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>39.1903</v>
+        <v>39.2</v>
       </c>
       <c r="G63" t="n">
         <v>80</v>
@@ -13270,7 +13414,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>55.29486493333332</v>
+        <v>55.30365813333331</v>
       </c>
       <c r="G66" t="n">
         <v>120</v>
@@ -13701,7 +13845,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>55.29485106666666</v>
+        <v>55.30354546666666</v>
       </c>
       <c r="G75" t="n">
         <v>120</v>
@@ -13897,7 +14041,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>110</v>
+        <v>109.9992</v>
       </c>
       <c r="G79" t="n">
         <v>110</v>
@@ -14093,7 +14237,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>33.9474</v>
+        <v>33.9468</v>
       </c>
       <c r="G83" t="n">
         <v>33.948</v>
@@ -14216,7 +14360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:N167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14285,6 +14429,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14340,6 +14489,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14395,6 +14549,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14450,6 +14609,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14505,6 +14669,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14560,6 +14729,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14615,6 +14789,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14670,6 +14849,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14725,6 +14909,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14780,6 +14969,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14835,6 +15029,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14890,6 +15089,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14945,6 +15149,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15000,6 +15209,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15055,6 +15269,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15110,6 +15329,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15165,6 +15389,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15220,6 +15449,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15275,6 +15509,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15330,6 +15569,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15385,6 +15629,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15440,6 +15689,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15495,6 +15749,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15550,6 +15809,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15605,6 +15869,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15660,6 +15929,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15715,6 +15989,11 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15770,6 +16049,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15825,6 +16109,11 @@
       <c r="M29" t="b">
         <v>1</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15880,6 +16169,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15935,6 +16229,11 @@
       <c r="M31" t="b">
         <v>1</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15990,6 +16289,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16045,6 +16349,11 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -16100,6 +16409,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16155,6 +16469,11 @@
       <c r="M35" t="b">
         <v>1</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16210,6 +16529,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16265,6 +16589,11 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -16320,6 +16649,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16375,6 +16709,11 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -16430,6 +16769,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16485,6 +16829,11 @@
       <c r="M41" t="b">
         <v>1</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16540,6 +16889,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16595,6 +16949,11 @@
       <c r="M43" t="b">
         <v>1</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16650,6 +17009,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16705,6 +17069,11 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16760,6 +17129,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16815,6 +17189,11 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16870,6 +17249,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16925,6 +17309,11 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16980,6 +17369,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17035,6 +17429,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17090,6 +17489,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17145,6 +17549,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17200,6 +17609,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17255,6 +17669,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17310,6 +17729,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17365,6 +17789,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -17399,10 +17828,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="I58" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="J58" t="n">
         <v>2</v>
@@ -17420,6 +17849,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17475,6 +17909,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17530,6 +17969,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17564,10 +18008,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="I61" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="J61" t="n">
         <v>2</v>
@@ -17585,6 +18029,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17640,6 +18089,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17674,10 +18128,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J63" t="n">
         <v>4</v>
@@ -17695,6 +18149,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17750,6 +18209,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17784,10 +18248,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="I65" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="J65" t="n">
         <v>2</v>
@@ -17805,6 +18269,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17860,6 +18329,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17894,10 +18368,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J67" t="n">
         <v>4</v>
@@ -17915,6 +18389,11 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17970,6 +18449,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18004,10 +18488,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="I69" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="J69" t="n">
         <v>2</v>
@@ -18025,6 +18509,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18080,6 +18569,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18114,10 +18608,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J71" t="n">
         <v>4</v>
@@ -18135,6 +18629,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18190,6 +18689,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18224,10 +18728,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="I73" t="n">
-        <v>6.6667</v>
+        <v>6.6666</v>
       </c>
       <c r="J73" t="n">
         <v>2</v>
@@ -18245,6 +18749,11 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18300,6 +18809,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18334,10 +18848,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J75" t="n">
         <v>4</v>
@@ -18355,6 +18869,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18410,6 +18929,11 @@
       <c r="M76" t="b">
         <v>1</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18444,10 +18968,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>5.857</v>
+        <v>5.867</v>
       </c>
       <c r="I77" t="n">
-        <v>5.857</v>
+        <v>5.867</v>
       </c>
       <c r="J77" t="n">
         <v>2</v>
@@ -18465,6 +18989,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18520,6 +19049,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18554,10 +19088,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>6.1055</v>
+        <v>6.1054</v>
       </c>
       <c r="I79" t="n">
-        <v>6.1055</v>
+        <v>6.1054</v>
       </c>
       <c r="J79" t="n">
         <v>4</v>
@@ -18575,6 +19109,11 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18630,6 +19169,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18685,6 +19229,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18719,10 +19268,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>6.1055</v>
+        <v>6.1054</v>
       </c>
       <c r="I82" t="n">
-        <v>6.1055</v>
+        <v>6.1054</v>
       </c>
       <c r="J82" t="n">
         <v>4</v>
@@ -18740,6 +19289,11 @@
       <c r="M82" t="b">
         <v>1</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18795,6 +19349,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18850,6 +19409,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18905,6 +19469,11 @@
       <c r="M85" t="b">
         <v>1</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -18960,6 +19529,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -19015,6 +19589,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19070,6 +19649,11 @@
       <c r="M88" t="b">
         <v>1</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -19125,6 +19709,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19180,6 +19769,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19235,6 +19829,11 @@
       <c r="M91" t="b">
         <v>1</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -19290,6 +19889,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19345,6 +19949,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19400,6 +20009,11 @@
       <c r="M94" t="b">
         <v>1</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19455,6 +20069,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19510,6 +20129,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19565,6 +20189,11 @@
       <c r="M97" t="b">
         <v>1</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19620,6 +20249,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19675,6 +20309,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19730,6 +20369,11 @@
       <c r="M100" t="b">
         <v>1</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19785,6 +20429,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19840,6 +20489,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19895,6 +20549,11 @@
       <c r="M103" t="b">
         <v>1</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19950,6 +20609,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -20005,6 +20669,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20060,6 +20729,11 @@
       <c r="M106" t="b">
         <v>1</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -20115,6 +20789,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20170,6 +20849,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20225,6 +20909,11 @@
       <c r="M109" t="b">
         <v>1</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -20280,6 +20969,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20335,6 +21029,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20390,6 +21089,11 @@
       <c r="M112" t="b">
         <v>1</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -20445,6 +21149,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20500,6 +21209,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20555,6 +21269,11 @@
       <c r="M115" t="b">
         <v>1</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -20610,6 +21329,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20665,6 +21389,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20720,6 +21449,11 @@
       <c r="M118" t="b">
         <v>1</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20775,6 +21509,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20830,6 +21569,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20864,10 +21608,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J121" t="n">
         <v>4</v>
@@ -20885,6 +21629,11 @@
       <c r="M121" t="b">
         <v>1</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -20940,6 +21689,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20995,6 +21749,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -21050,6 +21809,11 @@
       <c r="M124" t="b">
         <v>1</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -21084,10 +21848,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J125" t="n">
         <v>4</v>
@@ -21105,6 +21869,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21160,6 +21929,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21215,6 +21989,11 @@
       <c r="M127" t="b">
         <v>1</v>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -21270,6 +22049,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21304,10 +22088,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I129" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J129" t="n">
         <v>4</v>
@@ -21325,6 +22109,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21380,6 +22169,11 @@
       <c r="M130" t="b">
         <v>1</v>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21435,6 +22229,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21490,6 +22289,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21524,10 +22328,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I133" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J133" t="n">
         <v>4</v>
@@ -21545,6 +22349,11 @@
       <c r="M133" t="b">
         <v>1</v>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21600,6 +22409,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21655,6 +22469,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21710,6 +22529,11 @@
       <c r="M136" t="b">
         <v>1</v>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -21744,10 +22568,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I137" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J137" t="n">
         <v>4</v>
@@ -21765,6 +22589,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21820,6 +22649,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21875,6 +22709,11 @@
       <c r="M139" t="b">
         <v>1</v>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -21930,6 +22769,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21964,10 +22808,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J141" t="n">
         <v>4</v>
@@ -21985,6 +22829,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -22040,6 +22889,11 @@
       <c r="M142" t="b">
         <v>1</v>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -22095,6 +22949,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -22150,6 +23009,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -22184,10 +23048,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I145" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J145" t="n">
         <v>4</v>
@@ -22205,6 +23069,11 @@
       <c r="M145" t="b">
         <v>1</v>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -22260,6 +23129,11 @@
       <c r="M146" t="b">
         <v>1</v>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -22315,6 +23189,11 @@
       <c r="M147" t="b">
         <v>1</v>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -22370,6 +23249,11 @@
       <c r="M148" t="b">
         <v>1</v>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -22404,10 +23288,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J149" t="n">
         <v>4</v>
@@ -22425,6 +23309,11 @@
       <c r="M149" t="b">
         <v>1</v>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -22480,6 +23369,11 @@
       <c r="M150" t="b">
         <v>1</v>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -22535,6 +23429,11 @@
       <c r="M151" t="b">
         <v>1</v>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -22590,6 +23489,11 @@
       <c r="M152" t="b">
         <v>1</v>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -22624,10 +23528,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J153" t="n">
         <v>4</v>
@@ -22645,6 +23549,11 @@
       <c r="M153" t="b">
         <v>1</v>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -22700,6 +23609,11 @@
       <c r="M154" t="b">
         <v>1</v>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -22755,6 +23669,11 @@
       <c r="M155" t="b">
         <v>1</v>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -22810,6 +23729,11 @@
       <c r="M156" t="b">
         <v>1</v>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -22844,10 +23768,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J157" t="n">
         <v>4</v>
@@ -22865,6 +23789,11 @@
       <c r="M157" t="b">
         <v>1</v>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -22920,6 +23849,11 @@
       <c r="M158" t="b">
         <v>1</v>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -22975,6 +23909,11 @@
       <c r="M159" t="b">
         <v>1</v>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -23030,6 +23969,11 @@
       <c r="M160" t="b">
         <v>1</v>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -23064,10 +24008,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J161" t="n">
         <v>4</v>
@@ -23085,6 +24029,11 @@
       <c r="M161" t="b">
         <v>1</v>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -23140,6 +24089,11 @@
       <c r="M162" t="b">
         <v>1</v>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -23195,6 +24149,11 @@
       <c r="M163" t="b">
         <v>1</v>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -23250,6 +24209,11 @@
       <c r="M164" t="b">
         <v>1</v>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -23284,10 +24248,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="I165" t="n">
-        <v>9.166700000000001</v>
+        <v>9.166600000000001</v>
       </c>
       <c r="J165" t="n">
         <v>4</v>
@@ -23305,6 +24269,11 @@
       <c r="M165" t="b">
         <v>1</v>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -23360,6 +24329,11 @@
       <c r="M166" t="b">
         <v>1</v>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -23414,6 +24388,11 @@
       </c>
       <c r="M167" t="b">
         <v>1</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -23469,7 +24448,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13993.387779557</v>
+        <v>13993.515237225</v>
       </c>
     </row>
     <row r="3">
@@ -23489,7 +24468,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11135.16107714014</v>
+        <v>11135.26296024263</v>
       </c>
     </row>
     <row r="4">
@@ -23629,7 +24608,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.127311245430626</v>
+        <v>9.127394380824626</v>
       </c>
     </row>
     <row r="11">
@@ -23649,7 +24628,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.26300753757001</v>
+        <v>7.263073991726913</v>
       </c>
     </row>
     <row r="12">
@@ -23709,7 +24688,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31.3182351</v>
+        <v>31.3183275</v>
       </c>
     </row>
     <row r="15">
@@ -23729,7 +24708,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1607.4177</v>
+        <v>1607.4254</v>
       </c>
     </row>
     <row r="16">
@@ -23769,7 +24748,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11637.19362</v>
+        <v>11637.30763</v>
       </c>
     </row>
     <row r="18">
@@ -23809,7 +24788,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>134.4051395570001</v>
+        <v>134.4185872250001</v>
       </c>
     </row>
     <row r="20">
@@ -23889,7 +24868,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55.29469853333337</v>
+        <v>55.30230613333334</v>
       </c>
     </row>
     <row r="24">

--- a/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
+++ b/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11649,18 +11682,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11673,7 +11706,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11698,18 +11731,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11722,7 +11755,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11747,18 +11780,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11771,7 +11804,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11796,18 +11829,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.1363478260869565</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11820,7 +11853,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.136</t>
         </is>
       </c>
     </row>
@@ -11845,18 +11878,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11869,7 +11902,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11894,18 +11927,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.07568963210702342</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11918,7 +11951,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.076</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12111,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -12102,7 +12135,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12346,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -12337,7 +12370,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12548,11 +12581,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>30.82224430000005</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -12572,7 +12605,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12914,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -12905,7 +12938,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13443,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -13434,7 +13467,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13841,7 +13874,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -13865,7 +13898,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -17843,7 +17876,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M58" t="b">
@@ -17851,7 +17884,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18056,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M61" t="b">
@@ -18031,7 +18064,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18143,7 +18176,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M63" t="b">
@@ -18151,7 +18184,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18263,7 +18296,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M65" t="b">
@@ -18271,7 +18304,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18383,7 +18416,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M67" t="b">
@@ -18391,7 +18424,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18503,7 +18536,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M69" t="b">
@@ -18511,7 +18544,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18623,7 +18656,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M71" t="b">
@@ -18631,7 +18664,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18776,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M73" t="b">
@@ -18751,7 +18784,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18863,7 +18896,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M75" t="b">
@@ -18871,7 +18904,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -18983,7 +19016,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M77" t="b">
@@ -18991,7 +19024,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -19103,7 +19136,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M79" t="b">
@@ -19111,7 +19144,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -19283,7 +19316,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M82" t="b">
@@ -19291,7 +19324,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19496,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M85" t="b">
@@ -19471,7 +19504,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -19643,7 +19676,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M88" t="b">
@@ -19651,7 +19684,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -19823,7 +19856,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M91" t="b">
@@ -19831,7 +19864,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -20003,7 +20036,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M94" t="b">
@@ -20011,7 +20044,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -20183,7 +20216,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M97" t="b">
@@ -20191,7 +20224,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20396,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M100" t="b">
@@ -20371,7 +20404,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -20543,7 +20576,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M103" t="b">
@@ -20551,7 +20584,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20756,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M106" t="b">
@@ -20731,7 +20764,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -20903,7 +20936,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M109" t="b">
@@ -20911,7 +20944,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -21083,7 +21116,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M112" t="b">
@@ -21091,7 +21124,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -21263,7 +21296,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M115" t="b">
@@ -21271,7 +21304,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -21443,7 +21476,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M118" t="b">
@@ -21451,7 +21484,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -21623,7 +21656,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M121" t="b">
@@ -21631,7 +21664,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -21743,7 +21776,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M123" t="b">
@@ -21751,7 +21784,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -21863,7 +21896,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M125" t="b">
@@ -21871,7 +21904,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -21983,7 +22016,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M127" t="b">
@@ -21991,7 +22024,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -22103,7 +22136,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M129" t="b">
@@ -22111,7 +22144,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22256,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M131" t="b">
@@ -22231,7 +22264,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -22343,7 +22376,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M133" t="b">
@@ -22351,7 +22384,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -22463,7 +22496,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M135" t="b">
@@ -22471,7 +22504,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -22583,7 +22616,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M137" t="b">
@@ -22591,7 +22624,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -22703,7 +22736,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M139" t="b">
@@ -22711,7 +22744,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22856,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M141" t="b">
@@ -22831,7 +22864,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -22943,7 +22976,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M143" t="b">
@@ -22951,7 +22984,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -23063,7 +23096,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M145" t="b">
@@ -23071,7 +23104,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -23183,7 +23216,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M147" t="b">
@@ -23191,7 +23224,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -23303,7 +23336,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M149" t="b">
@@ -23311,7 +23344,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -23423,7 +23456,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M151" t="b">
@@ -23431,7 +23464,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -23543,7 +23576,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M153" t="b">
@@ -23551,7 +23584,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -23663,7 +23696,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M155" t="b">
@@ -23671,7 +23704,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -23783,7 +23816,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M157" t="b">
@@ -23791,7 +23824,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -23903,7 +23936,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M159" t="b">
@@ -23911,7 +23944,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -24023,7 +24056,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M161" t="b">
@@ -24031,7 +24064,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -24143,7 +24176,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M163" t="b">
@@ -24151,7 +24184,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -24263,7 +24296,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M165" t="b">
@@ -24271,7 +24304,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+          <t>срок поставки 4 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>
@@ -24383,7 +24416,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2034-01</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="M167" t="b">
@@ -24391,7 +24424,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>срок поставки 2 мес.; заказы с 2034-01</t>
+          <t>срок поставки 2 мес.; заказы с 2034-01; реактивный заказ — не раньше месяца наблюдения 2038-03</t>
         </is>
       </c>
     </row>

--- a/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
+++ b/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
+++ b/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
@@ -7538,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7647,6 +7647,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7722,6 +7727,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7797,6 +7805,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7872,6 +7883,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7947,6 +7961,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8022,6 +8039,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8097,6 +8117,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8172,6 +8195,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8247,6 +8273,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8322,6 +8351,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8397,6 +8429,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8472,6 +8507,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8547,6 +8585,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8622,6 +8663,9 @@
       <c r="U14" t="n">
         <v>1.97835</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8697,6 +8741,9 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8772,6 +8819,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8847,6 +8897,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8922,6 +8975,9 @@
       <c r="U18" t="n">
         <v>72.7974</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8997,6 +9053,9 @@
       <c r="U19" t="n">
         <v>16.5</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9072,6 +9131,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9147,6 +9209,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9222,6 +9287,9 @@
       <c r="U22" t="n">
         <v>28</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9297,6 +9365,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9372,6 +9443,9 @@
       <c r="U24" t="n">
         <v>15.3774</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9447,6 +9521,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9522,6 +9599,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9597,6 +9677,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9672,6 +9755,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9747,6 +9833,9 @@
       <c r="U29" t="n">
         <v>16.5</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9822,6 +9911,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9897,6 +9989,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9971,6 +10066,9 @@
       </c>
       <c r="U32" t="n">
         <v>11.8818</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9984,7 +10082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10048,6 +10146,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10090,6 +10193,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10132,6 +10238,9 @@
       <c r="L3" t="n">
         <v>1250</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10174,6 +10283,9 @@
       <c r="L4" t="n">
         <v>1430</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10216,6 +10328,9 @@
       <c r="L5" t="n">
         <v>1430</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10258,6 +10373,9 @@
       <c r="L6" t="n">
         <v>1430</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10299,6 +10417,9 @@
       </c>
       <c r="L7" t="n">
         <v>1430</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24538,7 +24659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24976,11 +25097,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -24996,11 +25117,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>55.30230613333334</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -25016,11 +25137,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>55.30230613333334</v>
       </c>
     </row>
     <row r="25">
@@ -25036,11 +25157,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -25056,7 +25177,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -25076,10 +25197,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25096,11 +25217,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>84</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -25116,10 +25237,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>83</v>
       </c>
     </row>

--- a/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
+++ b/results/reaction/P3_isru_zbo_reactive_MANDATORY_STRESS/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -870,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1396,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,24 +1416,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1441,29 +1443,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1473,29 +1475,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1505,176 +1507,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2556,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2483,6 +2638,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2554,6 +2715,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2625,6 +2792,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2696,6 +2869,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2767,6 +2946,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2838,6 +3023,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2909,6 +3100,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2980,6 +3177,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3051,6 +3254,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3122,6 +3331,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3193,6 +3408,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3264,6 +3485,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3335,6 +3562,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3406,6 +3639,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3477,6 +3716,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3548,6 +3793,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3619,6 +3870,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3690,6 +3947,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3761,6 +4024,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3832,6 +4101,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3903,6 +4178,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3974,6 +4255,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4045,6 +4332,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4116,6 +4409,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4187,6 +4486,12 @@
         <v>1.415606307500004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.59530225000007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4258,6 +4563,12 @@
         <v>1.435829962500004</v>
       </c>
       <c r="U27" t="n">
+        <v>39.93236316666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4329,6 +4640,12 @@
         <v>1.456053617500004</v>
       </c>
       <c r="U28" t="n">
+        <v>40.2694240833334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4400,6 +4717,12 @@
         <v>1.476277272500004</v>
       </c>
       <c r="U29" t="n">
+        <v>40.60648500000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4471,6 +4794,12 @@
         <v>1.496500927500004</v>
       </c>
       <c r="U30" t="n">
+        <v>40.94354591666674</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4542,6 +4871,12 @@
         <v>1.516724582500004</v>
       </c>
       <c r="U31" t="n">
+        <v>41.2806068333334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4613,6 +4948,12 @@
         <v>1.553711264000004</v>
       </c>
       <c r="U32" t="n">
+        <v>42.17643530000007</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4684,6 +5025,12 @@
         <v>1.607460972000004</v>
       </c>
       <c r="U33" t="n">
+        <v>43.07226376666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4755,6 +5102,12 @@
         <v>1.661210680000003</v>
       </c>
       <c r="U34" t="n">
+        <v>43.96809223333339</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4826,6 +5179,12 @@
         <v>1.714960388000003</v>
       </c>
       <c r="U35" t="n">
+        <v>44.86392070000006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4897,6 +5256,12 @@
         <v>1.768710096000003</v>
       </c>
       <c r="U36" t="n">
+        <v>45.75974916666672</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4968,6 +5333,12 @@
         <v>1.822459804000003</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65557763333339</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5039,6 +5410,12 @@
         <v>1.530160016000003</v>
       </c>
       <c r="U38" t="n">
+        <v>44.14142290000005</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5110,6 +5487,12 @@
         <v>0.8918107320000032</v>
       </c>
       <c r="U39" t="n">
+        <v>33.50226816666672</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5181,6 +5564,12 @@
         <v>0.416481448000003</v>
       </c>
       <c r="U40" t="n">
+        <v>28.29711343333338</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5252,6 +5641,12 @@
         <v>0.1301634030000015</v>
       </c>
       <c r="U41" t="n">
+        <v>23.09195870000005</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5323,6 +5718,12 @@
         <v>0.04144338199999997</v>
       </c>
       <c r="U42" t="n">
+        <v>25.3397794</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5394,6 +5795,12 @@
         <v>0.1243301459999999</v>
       </c>
       <c r="U43" t="n">
+        <v>26.72122546666666</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5465,6 +5872,12 @@
         <v>0.4789149339999998</v>
       </c>
       <c r="U44" t="n">
+        <v>37.15927233333333</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5536,6 +5949,12 @@
         <v>1.105197745999999</v>
       </c>
       <c r="U45" t="n">
+        <v>47.59731919999999</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5607,6 +6026,12 @@
         <v>1.731480557999999</v>
       </c>
       <c r="U46" t="n">
+        <v>58.03536606666665</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5678,6 +6103,12 @@
         <v>2.334063226</v>
       </c>
       <c r="U47" t="n">
+        <v>67.68340813333333</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5749,6 +6180,12 @@
         <v>2.648313902</v>
       </c>
       <c r="U48" t="n">
+        <v>68.5103886</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5820,6 +6257,12 @@
         <v>2.69793273</v>
       </c>
       <c r="U49" t="n">
+        <v>69.33736906666667</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5891,6 +6334,12 @@
         <v>2.747553700000001</v>
       </c>
       <c r="U50" t="n">
+        <v>76.87275426666667</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5962,6 +6411,12 @@
         <v>2.797176812</v>
       </c>
       <c r="U51" t="n">
+        <v>77.69980613333334</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6033,6 +6488,12 @@
         <v>2.846799924</v>
       </c>
       <c r="U52" t="n">
+        <v>78.526858</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6104,6 +6565,12 @@
         <v>2.896423036</v>
       </c>
       <c r="U53" t="n">
+        <v>79.35390986666667</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6175,6 +6642,12 @@
         <v>2.946046147999999</v>
       </c>
       <c r="U54" t="n">
+        <v>80.18096173333333</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6246,6 +6719,12 @@
         <v>2.99566926</v>
       </c>
       <c r="U55" t="n">
+        <v>81.0080136</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6317,6 +6796,12 @@
         <v>3.045292371999999</v>
       </c>
       <c r="U56" t="n">
+        <v>81.83506546666666</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6388,6 +6873,12 @@
         <v>3.094915483999999</v>
       </c>
       <c r="U57" t="n">
+        <v>82.66211733333333</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6459,6 +6950,12 @@
         <v>3.144538595999999</v>
       </c>
       <c r="U58" t="n">
+        <v>83.48916919999999</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6530,6 +7027,12 @@
         <v>3.194161707999999</v>
       </c>
       <c r="U59" t="n">
+        <v>84.31622106666666</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6601,6 +7104,12 @@
         <v>3.243784819999999</v>
       </c>
       <c r="U60" t="n">
+        <v>85.14327293333332</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6672,6 +7181,12 @@
         <v>3.293407931999999</v>
       </c>
       <c r="U61" t="n">
+        <v>85.97032479999999</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6743,6 +7258,12 @@
         <v>3.318216107999998</v>
       </c>
       <c r="U62" t="n">
+        <v>92.67854546666665</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6814,6 +7335,12 @@
         <v>3.318209348</v>
       </c>
       <c r="U63" t="n">
+        <v>92.6784328</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6885,6 +7412,12 @@
         <v>3.318202588</v>
       </c>
       <c r="U64" t="n">
+        <v>92.67832013333333</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6956,6 +7489,12 @@
         <v>3.318195828</v>
       </c>
       <c r="U65" t="n">
+        <v>92.67820746666666</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7027,6 +7566,12 @@
         <v>3.318189068</v>
       </c>
       <c r="U66" t="n">
+        <v>92.6780948</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7098,6 +7643,12 @@
         <v>3.318182308</v>
       </c>
       <c r="U67" t="n">
+        <v>92.67798213333333</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7169,6 +7720,12 @@
         <v>3.318175548</v>
       </c>
       <c r="U68" t="n">
+        <v>92.67786946666666</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7240,6 +7797,12 @@
         <v>3.318168788</v>
       </c>
       <c r="U69" t="n">
+        <v>92.6777568</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7311,6 +7874,12 @@
         <v>3.318162028</v>
       </c>
       <c r="U70" t="n">
+        <v>92.67764413333333</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7382,6 +7951,12 @@
         <v>3.318155268</v>
       </c>
       <c r="U71" t="n">
+        <v>92.67753146666666</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7453,6 +8028,12 @@
         <v>3.318148508</v>
       </c>
       <c r="U72" t="n">
+        <v>92.6774188</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7524,6 +8105,12 @@
         <v>3.318141748</v>
       </c>
       <c r="U73" t="n">
+        <v>92.67730613333333</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10173,7 +10760,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10182,13 +10769,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -10546,7 +11133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12372,7 +12959,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12380,14 +12967,14 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G39" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -12404,7 +12991,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12421,7 +13008,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12429,14 +13016,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>109.876</v>
       </c>
       <c r="G40" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -12470,7 +13057,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12478,18 +13065,19 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -12499,7 +13087,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12514,7 +13106,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12522,7 +13114,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -12558,27 +13150,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -12588,11 +13179,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12607,7 +13194,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12615,14 +13202,14 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G44" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -12639,7 +13226,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12656,7 +13243,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12664,14 +13251,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G45" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -12688,7 +13275,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12705,7 +13292,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12713,170 +13300,170 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G46" t="n">
+        <v>190</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G47" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46">
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48">
         <f>=</f>
         <v/>
       </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D49" t="n">
         <v>2036</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47">
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49">
         <f>=</f>
         <v/>
       </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>25.44727350000007</v>
-      </c>
-      <c r="G48" t="n">
-        <v>70</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>190</v>
-      </c>
-      <c r="G49" t="n">
-        <v>190</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I49" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12891,7 +13478,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -12899,14 +13486,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>190</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G50" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -12923,7 +13510,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12940,7 +13527,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -12948,14 +13535,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>13.189</v>
+        <v>41.2806068333334</v>
       </c>
       <c r="G51" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -12972,7 +13559,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12989,7 +13576,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -12997,14 +13584,14 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G52" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -13021,7 +13608,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13625,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -13046,219 +13633,219 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>190</v>
+      </c>
+      <c r="G53" t="n">
+        <v>190</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G54" t="n">
+        <v>110</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G55" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53">
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56">
         <f>=</f>
         <v/>
       </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D57" t="n">
         <v>2037</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57">
         <f>=</f>
         <v/>
       </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>45.37903573333334</v>
-      </c>
-      <c r="G55" t="n">
-        <v>120</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I55" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="G56" t="n">
-        <v>190</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I56" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>161.7714</v>
-      </c>
-      <c r="G57" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13273,7 +13860,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -13281,14 +13868,14 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>110</v>
+        <v>45.37903573333334</v>
       </c>
       <c r="G58" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -13305,7 +13892,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13322,7 +13909,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -13330,14 +13917,14 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>48.87720000000001</v>
+        <v>69.33736906666667</v>
       </c>
       <c r="G59" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -13354,7 +13941,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13379,14 +13966,14 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>120</v>
+        <v>161.772</v>
       </c>
       <c r="G60" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -13403,7 +13990,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13428,14 +14015,14 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>100</v>
+        <v>161.7714</v>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>161.772</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -13452,7 +14039,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13477,14 +14064,14 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>reserved_E_t_per_year</t>
+          <t>reserved_B_t_per_year</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="G62" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -13501,7 +14088,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Earth-Flex</t>
         </is>
       </c>
     </row>
@@ -13526,14 +14113,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ordered_E_t</t>
+          <t>ordered_B_t</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>39.2</v>
+        <v>48.87720000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -13550,7 +14137,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Earth-Flex</t>
         </is>
       </c>
     </row>
@@ -13567,7 +14154,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -13575,268 +14162,268 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>120</v>
+      </c>
+      <c r="G64" t="n">
+        <v>120</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>100</v>
+      </c>
+      <c r="G65" t="n">
+        <v>100</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>reserved_E_t_per_year</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>80</v>
+      </c>
+      <c r="G66" t="n">
+        <v>80</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ordered_E_t</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>80</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64">
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68">
         <f>=</f>
         <v/>
       </c>
-      <c r="I64" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D69" t="n">
         <v>2038</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65">
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69">
         <f>=</f>
         <v/>
       </c>
-      <c r="I65" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>55.30365813333331</v>
-      </c>
-      <c r="G66" t="n">
-        <v>120</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>190</v>
-      </c>
-      <c r="G67" t="n">
-        <v>190</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>190</v>
-      </c>
-      <c r="G68" t="n">
-        <v>190</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>102.516</v>
-      </c>
-      <c r="G69" t="n">
-        <v>110</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13851,7 +14438,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -13859,14 +14446,14 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>102.5148</v>
+        <v>55.30365813333331</v>
       </c>
       <c r="G70" t="n">
-        <v>102.516</v>
+        <v>120</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -13883,7 +14470,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13900,7 +14487,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -13908,11 +14495,11 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>120</v>
+        <v>85.97032479999999</v>
       </c>
       <c r="G71" t="n">
         <v>120</v>
@@ -13932,7 +14519,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13949,7 +14536,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -13957,14 +14544,14 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G72" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -13981,7 +14568,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13998,7 +14585,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -14006,317 +14593,317 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>190</v>
+      </c>
+      <c r="G73" t="n">
+        <v>190</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>102.516</v>
+      </c>
+      <c r="G74" t="n">
+        <v>110</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>102.5148</v>
+      </c>
+      <c r="G75" t="n">
+        <v>102.516</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>120</v>
+      </c>
+      <c r="G76" t="n">
+        <v>120</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>120</v>
+      </c>
+      <c r="G77" t="n">
+        <v>120</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73">
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78">
         <f>=</f>
         <v/>
       </c>
-      <c r="I73" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D79" t="n">
         <v>2039</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74">
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79">
         <f>=</f>
         <v/>
       </c>
-      <c r="I74" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>55.30354546666666</v>
-      </c>
-      <c r="G75" t="n">
-        <v>120</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>2040-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>190</v>
-      </c>
-      <c r="G76" t="n">
-        <v>190</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>190</v>
-      </c>
-      <c r="G77" t="n">
-        <v>190</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>110</v>
-      </c>
-      <c r="G78" t="n">
-        <v>110</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>109.9992</v>
-      </c>
-      <c r="G79" t="n">
-        <v>110</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I79" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -14331,7 +14918,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -14339,11 +14926,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>120</v>
+        <v>55.30354546666666</v>
       </c>
       <c r="G80" t="n">
         <v>120</v>
@@ -14363,7 +14950,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14967,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -14388,11 +14975,11 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>120</v>
+        <v>92.67854546666665</v>
       </c>
       <c r="G81" t="n">
         <v>120</v>
@@ -14412,7 +14999,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14437,14 +15024,14 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>reserved_E_t_per_year</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>33.948</v>
+        <v>190</v>
       </c>
       <c r="G82" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -14461,7 +15048,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14486,14 +15073,14 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ordered_E_t</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>33.9468</v>
+        <v>190</v>
       </c>
       <c r="G83" t="n">
-        <v>33.948</v>
+        <v>190</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -14510,7 +15097,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Emergency</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14527,7 +15114,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -14535,72 +15122,366 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>110</v>
+      </c>
+      <c r="G84" t="n">
+        <v>110</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>109.9992</v>
+      </c>
+      <c r="G85" t="n">
+        <v>110</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>120</v>
+      </c>
+      <c r="G86" t="n">
+        <v>120</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>120</v>
+      </c>
+      <c r="G87" t="n">
+        <v>120</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>reserved_E_t_per_year</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>33.948</v>
+      </c>
+      <c r="G88" t="n">
+        <v>80</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ordered_E_t</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>33.9468</v>
+      </c>
+      <c r="G89" t="n">
+        <v>33.948</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84">
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90">
         <f>=</f>
         <v/>
       </c>
-      <c r="I84" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="I90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>MANDATORY_STRESS</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo_reactive</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D91" t="n">
         <v>2040</v>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85">
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91">
         <f>=</f>
         <v/>
       </c>
-      <c r="I85" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="I91" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24659,7 +25540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24701,7 +25582,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13993.515237225</v>
+        <v>13993.885102995</v>
       </c>
     </row>
     <row r="3">
@@ -24721,7 +25602,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11135.26296024263</v>
+        <v>11135.63282601263</v>
       </c>
     </row>
     <row r="4">
@@ -24861,7 +25742,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.127394380824626</v>
+        <v>9.12763562905236</v>
       </c>
     </row>
     <row r="11">
@@ -24881,7 +25762,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.263073991726913</v>
+        <v>7.263315239954649</v>
       </c>
     </row>
     <row r="12">
@@ -25041,7 +25922,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>134.4185872250001</v>
+        <v>134.7884529950001</v>
       </c>
     </row>
     <row r="20">
@@ -25157,11 +26038,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -25177,11 +26058,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -25197,11 +26078,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -25217,10 +26098,10 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25237,11 +26118,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -25257,11 +26138,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MANDATORY_STRESS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo_reactive</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>83</v>
+      <c r="D32" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
